--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1200,8 +1200,6 @@
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -1604,7 +1602,7 @@
         <v>11</v>
       </c>
       <c r="L9" t="n">
-        <v>63.6</v>
+        <v>72.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -6924,13 +6922,18 @@
           <t>INLET ID FAN 2 PRESSURE TRANSMITTER 10HNA62CP001</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -23553,7 +23556,7 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -24997,7 +25000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -25089,6 +25092,11 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25106,11 +25114,7 @@
           <t>ACTUATOR FEED WATER CONTROL VALVE 100% 10LAB30AA210</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10LAB30AA210</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1</v>
       </c>
@@ -25141,6 +25145,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25188,6 +25197,11 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25235,6 +25249,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25282,6 +25301,11 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25329,6 +25353,11 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25376,6 +25405,11 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25428,6 +25462,11 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>WO-100826-0028</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25475,6 +25514,11 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>WO-100826-0029</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25527,6 +25571,11 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25579,6 +25628,11 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>WO-100826-0161</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25631,6 +25685,11 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25678,6 +25737,11 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>WO-100826-0161</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25730,6 +25794,11 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25777,6 +25846,11 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>WO-100826-0161</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25824,6 +25898,11 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25871,6 +25950,11 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25918,6 +26002,11 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25965,6 +26054,11 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -26012,6 +26106,11 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -26059,6 +26158,11 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>WO-100826-0036</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -26106,6 +26210,11 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -26153,6 +26262,11 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -26200,6 +26314,11 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -26252,6 +26371,11 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>WO-100826-0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -26304,6 +26428,11 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>WO-100826-0026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -26351,6 +26480,11 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -26398,6 +26532,11 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -26445,6 +26584,11 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -26497,6 +26641,11 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -26544,6 +26693,11 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26596,6 +26750,11 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -26648,6 +26807,11 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26690,6 +26854,11 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26737,6 +26906,11 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26789,6 +26963,11 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26841,6 +27020,11 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26888,6 +27072,11 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26930,6 +27119,11 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>WO-100826-0053</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26972,6 +27166,11 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>WO-100826-0053</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -27024,6 +27223,11 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -27076,6 +27280,11 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -27118,6 +27327,11 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27160,6 +27374,11 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -27207,6 +27426,11 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -27254,6 +27478,11 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -27301,6 +27530,11 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -27348,6 +27582,11 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -27395,6 +27634,11 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -27442,6 +27686,11 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27489,6 +27738,11 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -27536,6 +27790,11 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -27583,6 +27842,11 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -27630,6 +27894,11 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -27682,6 +27951,11 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -27729,6 +28003,11 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>WO-100826-0063</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -27776,6 +28055,11 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>WO-100826-0063</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -27828,6 +28112,11 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>WO-100826-0073</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -27880,6 +28169,11 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>WO-100826-0073</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27927,6 +28221,11 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27969,6 +28268,11 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>WO-100826-0063</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28016,6 +28320,11 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>WO-100826-0060</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -28063,6 +28372,11 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -28110,6 +28424,11 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -28157,6 +28476,11 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -28204,6 +28528,11 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -28251,6 +28580,11 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -28298,6 +28632,11 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -28345,6 +28684,11 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -28392,6 +28736,11 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>WO-100826-0059</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -28439,6 +28788,11 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -28486,6 +28840,11 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -28533,6 +28892,11 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -28575,6 +28939,11 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -28622,6 +28991,11 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -28669,6 +29043,11 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -28711,6 +29090,11 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -28753,6 +29137,11 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>WO-100826-0063</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -28800,6 +29189,11 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -28847,6 +29241,11 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>WO-100826-0031</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -28889,6 +29288,11 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -28931,6 +29335,11 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -28973,6 +29382,11 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -29015,6 +29429,11 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -29057,6 +29476,11 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -29099,6 +29523,11 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -29141,6 +29570,11 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -29183,6 +29617,11 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -29225,6 +29664,11 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -29267,6 +29711,11 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -29309,6 +29758,11 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -29356,6 +29810,11 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -29403,6 +29862,11 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -29449,6 +29913,11 @@
       </c>
       <c r="O94" t="n">
         <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -29463,7 +29932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29540,6 +30009,16 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Calibration_TRUE_FALSE</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -29576,6 +30055,11 @@
       </c>
       <c r="M2" t="b">
         <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WO-100826-0161</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -29619,6 +30103,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -29661,6 +30150,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -29703,6 +30197,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -29737,6 +30236,11 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -29774,6 +30278,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>WO-100826-0047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -29816,6 +30325,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WO-100826-0047</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -29858,6 +30372,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WO-100826-0047</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -29900,6 +30419,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -29942,6 +30466,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WO-100826-0031</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -29984,6 +30513,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WO-100826-0031</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -30026,6 +30560,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WO-100826-0032</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -30068,6 +30607,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -30110,6 +30654,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -30149,6 +30698,11 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -30188,6 +30742,11 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -30227,6 +30786,11 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -30269,6 +30833,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -30308,6 +30877,11 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>WO-100826-0022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -30342,6 +30916,11 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WO-100826-0024</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -30379,6 +30958,11 @@
       <c r="M22" t="b">
         <v>0</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>WO-100826-0026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -30421,6 +31005,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -30463,6 +31052,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -30505,6 +31099,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -30547,6 +31146,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -30589,6 +31193,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -30628,6 +31237,11 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -30667,6 +31281,11 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -30706,6 +31325,11 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>WO-100826-0048</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -30740,6 +31364,11 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>WO-100826-0052</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -30774,6 +31403,11 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -30816,6 +31450,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -30858,6 +31497,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -30897,6 +31541,11 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -30936,6 +31585,11 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -30978,6 +31632,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -31020,6 +31679,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -31062,6 +31726,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -31104,6 +31773,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -31143,6 +31817,11 @@
       <c r="L41" t="n">
         <v>0</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -31177,6 +31856,11 @@
       <c r="L42" t="n">
         <v>0</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -31216,6 +31900,11 @@
       <c r="L43" t="n">
         <v>0</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -31258,6 +31947,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -31300,6 +31994,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -31342,6 +32041,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -31384,6 +32088,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -31426,6 +32135,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -31468,6 +32182,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -31510,6 +32229,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -31552,6 +32276,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -31594,6 +32323,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -31636,6 +32370,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -31678,6 +32417,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -31720,6 +32464,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -31754,6 +32503,11 @@
       <c r="L56" t="n">
         <v>0</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -31788,6 +32542,11 @@
       <c r="L57" t="n">
         <v>0</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -31830,6 +32589,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -31872,6 +32636,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -31914,6 +32683,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -31956,6 +32730,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -31998,6 +32777,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -32040,6 +32824,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -32074,6 +32863,11 @@
       <c r="L64" t="n">
         <v>0</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -32116,6 +32910,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -32158,6 +32957,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>WO-100826-0063</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -32192,6 +32996,11 @@
       <c r="L67" t="n">
         <v>0</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -32234,6 +33043,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -32276,6 +33090,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -32318,6 +33137,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -32360,6 +33184,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -32402,6 +33231,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -32444,6 +33278,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -32486,6 +33325,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -32528,6 +33372,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -32562,6 +33411,11 @@
       <c r="L76" t="n">
         <v>0</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -32604,6 +33458,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>WO-100826-0056</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -32646,6 +33505,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>WO-100826-0056</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -32688,6 +33552,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>WO-100826-0056</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -32730,6 +33599,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>WO-100826-0073</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -32772,6 +33646,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -32806,6 +33685,11 @@
       <c r="L82" t="n">
         <v>0</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -32840,6 +33724,11 @@
       <c r="L83" t="n">
         <v>0</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -32874,6 +33763,11 @@
       <c r="L84" t="n">
         <v>0</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -32918,6 +33812,11 @@
       <c r="L85" t="n">
         <v>0</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -32952,6 +33851,11 @@
       <c r="L86" t="n">
         <v>0</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -32986,6 +33890,11 @@
       <c r="L87" t="n">
         <v>0</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -33020,6 +33929,11 @@
       <c r="L88" t="n">
         <v>0</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -33053,6 +33967,11 @@
       </c>
       <c r="L89" t="n">
         <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -33067,7 +33986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -33143,6 +34062,16 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Calibration_TRUE_FALSE</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -33179,6 +34108,11 @@
       </c>
       <c r="M2" t="b">
         <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -33217,6 +34151,11 @@
       <c r="M3" t="b">
         <v>0</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -33254,6 +34193,11 @@
       <c r="M4" t="b">
         <v>0</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -33291,6 +34235,11 @@
       <c r="M5" t="b">
         <v>0</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -33328,6 +34277,11 @@
       <c r="M6" t="b">
         <v>0</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -33365,6 +34319,11 @@
       <c r="M7" t="b">
         <v>0</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -33402,6 +34361,11 @@
       <c r="M8" t="b">
         <v>0</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -33436,6 +34400,11 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -33470,6 +34439,11 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -33504,6 +34478,11 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -33538,6 +34517,11 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WO-100826-0052</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -33575,6 +34559,11 @@
       <c r="M13" t="b">
         <v>0</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -33612,6 +34601,11 @@
       <c r="M14" t="b">
         <v>0</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -33649,6 +34643,11 @@
       <c r="M15" t="b">
         <v>0</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -33686,6 +34685,11 @@
       <c r="M16" t="b">
         <v>0</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -33720,6 +34724,11 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -33754,6 +34763,11 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -33788,6 +34802,11 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -33822,6 +34841,11 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -33856,6 +34880,11 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WO-100826-0062</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -33890,6 +34919,11 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>WO-100826-0062</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -33924,6 +34958,11 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>WO-100826-0062</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -33958,6 +34997,11 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>WO-100826-0062</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -33992,6 +35036,11 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>WO-100826-0057</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -34026,6 +35075,11 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -34068,6 +35122,11 @@
       <c r="M27" t="b">
         <v>0</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -34102,6 +35161,11 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -34136,6 +35200,11 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -34170,6 +35239,11 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -34204,6 +35278,11 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -34238,6 +35317,11 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -34271,6 +35355,11 @@
       </c>
       <c r="L33" t="n">
         <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -34285,7 +35374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34408,6 +35497,16 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Calibration_TRUE_FALSE</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -34469,6 +35568,11 @@
       </c>
       <c r="U2" t="b">
         <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -34532,6 +35636,11 @@
       <c r="U3" t="b">
         <v>1</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -34594,6 +35703,11 @@
       <c r="U4" t="b">
         <v>1</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -34656,6 +35770,11 @@
       <c r="U5" t="b">
         <v>1</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -34718,6 +35837,11 @@
       <c r="U6" t="b">
         <v>1</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>WO-100826-0031</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -34780,6 +35904,11 @@
       <c r="U7" t="b">
         <v>1</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>WO-100826-0031</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -34842,6 +35971,11 @@
       <c r="U8" t="b">
         <v>1</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>WO-100826-0031</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -34904,6 +36038,11 @@
       <c r="U9" t="b">
         <v>1</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -34966,6 +36105,11 @@
       <c r="U10" t="b">
         <v>1</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -35028,6 +36172,11 @@
       <c r="U11" t="b">
         <v>1</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -35090,6 +36239,11 @@
       <c r="U12" t="b">
         <v>1</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>WO-100826-0021</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -35152,6 +36306,11 @@
       <c r="U13" t="b">
         <v>1</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>WO-100826-0021</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -35214,6 +36373,11 @@
       <c r="U14" t="b">
         <v>1</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>WO-100826-0021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -35276,6 +36440,11 @@
       <c r="U15" t="b">
         <v>1</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>WO-100826-0021</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -35338,6 +36507,11 @@
       <c r="U16" t="b">
         <v>1</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>WO-100826-0023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -35400,6 +36574,11 @@
       <c r="U17" t="b">
         <v>1</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>WO-100826-0023</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -35462,6 +36641,11 @@
       <c r="U18" t="b">
         <v>1</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>WO-100826-0023</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -35524,6 +36708,11 @@
       <c r="U19" t="b">
         <v>1</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>WO-100826-0025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -35586,6 +36775,11 @@
       <c r="U20" t="b">
         <v>1</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>WO-100826-0025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -35648,6 +36842,11 @@
       <c r="U21" t="b">
         <v>1</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>WO-100826-0025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -35710,6 +36909,11 @@
       <c r="U22" t="b">
         <v>1</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>WO-100826-0025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -35772,6 +36976,11 @@
       <c r="U23" t="b">
         <v>1</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>WO-100826-0025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -35834,6 +37043,11 @@
       <c r="U24" t="b">
         <v>1</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>WO-100826-0027</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -35896,6 +37110,11 @@
       <c r="U25" t="b">
         <v>1</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>WO-100826-0027</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -35958,6 +37177,11 @@
       <c r="U26" t="b">
         <v>1</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>WO-100826-0027</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -36020,6 +37244,11 @@
       <c r="U27" t="b">
         <v>1</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>WO-100826-0027</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -36067,6 +37296,11 @@
       <c r="U28" t="b">
         <v>0</v>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -36114,6 +37348,11 @@
       <c r="U29" t="b">
         <v>0</v>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>WO-100826-0036</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -36166,6 +37405,11 @@
       <c r="U30" t="b">
         <v>0</v>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>WO-100826-0054</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -36227,6 +37471,11 @@
       </c>
       <c r="U31" t="b">
         <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -25114,7 +25114,6 @@
           <t>ACTUATOR FEED WATER CONTROL VALVE 100% 10LAB30AA210</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1</v>
       </c>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
@@ -2503,9 +2503,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2517,7 +2522,7 @@
         <v>19</v>
       </c>
       <c r="L24" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2933,10 +2938,10 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
-        <v>65</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -3161,10 +3166,10 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L35" t="n">
-        <v>85.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3216,7 +3221,7 @@
         <v>13</v>
       </c>
       <c r="L36" t="n">
-        <v>84.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3497,9 +3502,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3511,7 +3521,7 @@
         <v>21</v>
       </c>
       <c r="L41" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3554,9 +3564,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3565,10 +3580,10 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3617,10 +3632,10 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3663,9 +3678,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3677,7 +3697,7 @@
         <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3772,9 +3792,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3786,7 +3811,7 @@
         <v>4</v>
       </c>
       <c r="L46" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4270,9 +4295,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4284,7 +4314,7 @@
         <v>13</v>
       </c>
       <c r="L55" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4448,7 +4478,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4460,7 +4490,7 @@
         <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4897,7 +4927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H755"/>
+  <dimension ref="A1:H749"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11233,13 +11263,18 @@
           <t>UNIT 1 ESP TRAFO 1 (GENERAL CLEANING, INSPEKSI, IR TEST)</t>
         </is>
       </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="D229" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -11256,13 +11291,18 @@
           <t>UNIT 1 ESP TRAFO 2 (GENERAL CLEANING, INSPEKSI, IR TEST)</t>
         </is>
       </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="D230" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -11279,13 +11319,18 @@
           <t>UNIT 1 ESP TRAFO 3 (GENERAL CLEANING, INSPEKSI, IR TEST)</t>
         </is>
       </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -11302,13 +11347,18 @@
           <t>UNIT 1 ESP TRAFO 4 (GENERAL CLEANING, INSPEKSI, IR TEST)</t>
         </is>
       </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="D232" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -11325,13 +11375,18 @@
           <t>UNIT 1 ESP TRAFO 5 (GENERAL CLEANING, INSPEKSI, IR TEST)</t>
         </is>
       </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -11348,13 +11403,18 @@
           <t>UNIT 1 ESP TRAFO 6 (GENERAL CLEANING, INSPEKSI, IR TEST)</t>
         </is>
       </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="D234" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -13965,13 +14025,18 @@
           <t>INSPECTION BRUSH GROUNDING</t>
         </is>
       </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E328" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14016,13 +14081,18 @@
           <t>INSPECTION HEATER NEUTRAL SIDE CUBICLE</t>
         </is>
       </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="D330" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14039,13 +14109,18 @@
           <t>INSPECTION HEATER LINE SIDE CUBICLE</t>
         </is>
       </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="D331" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E331" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14085,13 +14160,18 @@
           <t>ASSEMBLY BRACKET SISI FRONT</t>
         </is>
       </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="D333" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -14108,13 +14188,18 @@
           <t>ASSEMBLY BRACKET SISI REAR</t>
         </is>
       </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14589,7 +14674,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>INSPECTION CONTACT RESISTANCE BUSDUCT</t>
+          <t>CLEANING</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -14607,12 +14692,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>WO-100826-0041</t>
+          <t>WO-100826-0042</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>INSPECTION ISOLATION RESISTANCE BUSDUCT</t>
+          <t>INSPECTION ISOLATOR BUSHING</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -14621,7 +14711,7 @@
         </is>
       </c>
       <c r="E353" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -14630,12 +14720,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>WO-100826-0041</t>
+          <t>WO-100826-0042</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>CLEANING</t>
+          <t>INSPECTION TERMINASI</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -14644,7 +14739,7 @@
         </is>
       </c>
       <c r="E354" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -14658,7 +14753,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>INSPECTION ISOLATOR BUSHING</t>
+          <t>CLEANING BUSHING CONNECTION HV &amp; LV</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -14686,7 +14781,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>INSPECTION TERMINASI</t>
+          <t>INSPECTION And CLEANING PANEL</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -14714,7 +14809,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>CLEANING BUSHING CONNECTION HV &amp; LV</t>
+          <t>INSPECTION SILICAGEL</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -14742,7 +14837,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>INSPECTION And CLEANING PANEL</t>
+          <t>INSPECTION GROUNDING SYSTEM</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -14770,7 +14865,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>INSPECTION SILICAGEL</t>
+          <t>TRANSFORMER OIL LEAKAGE INSPECTION</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -14798,7 +14893,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>INSPECTION GROUNDING SYSTEM</t>
+          <t>PROTECTIVE DEVICE TEST AND TRANSFORMER RESET</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -14826,7 +14921,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>TRANSFORMER OIL LEAKAGE INSPECTION</t>
+          <t>INSPECTION PANEL TAP CHANGER</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -14854,7 +14949,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PROTECTIVE DEVICE TEST AND TRANSFORMER RESET</t>
+          <t>TRANSFORMER WINDING INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -14882,7 +14977,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>INSPECTION PANEL TAP CHANGER</t>
+          <t>RDS TEST</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -14910,7 +15005,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>TRANSFORMER WINDING INSULATION RESISTANCE INSPECTION</t>
+          <t>MECHANICAL RELAY TEST</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -14938,7 +15033,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RDS TEST</t>
+          <t>INSPECTION DISCONNECTING SWITCH NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -14966,7 +15061,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MECHANICAL RELAY TEST</t>
+          <t>INSPECTION TRAFO NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -14994,7 +15089,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>INSPECTION DISCONNECTING SWITCH NETRAL GROUNDING RESISTANCE (NGR)</t>
+          <t>INSPECTION ISOLATOR BUSHING NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -15022,7 +15117,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>INSPECTION TRAFO NETRAL GROUNDING RESISTANCE (NGR)</t>
+          <t>INSPECTION TERMINASI NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -15050,7 +15145,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>INSPECTION ISOLATOR BUSHING NETRAL GROUNDING RESISTANCE (NGR)</t>
+          <t>INSPECTION GROUNDING SYSTEM NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -15078,7 +15173,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>INSPECTION TERMINASI NETRAL GROUNDING RESISTANCE (NGR)</t>
+          <t>INSPECTION HEATER BUSDUCT</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -15106,12 +15201,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>INSPECTION GROUNDING SYSTEM NETRAL GROUNDING RESISTANCE (NGR)</t>
+          <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -15134,7 +15229,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>INSPECTION HEATER BUSDUCT</t>
+          <t>INSPECTION SILICA BUSDUCT</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -15162,12 +15257,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
+          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -15190,12 +15285,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>INSPECTION SILICA BUSDUCT</t>
+          <t>CLEANING</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -15213,17 +15308,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>WO-100826-0042</t>
+          <t>WO-100826-0043</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
+          <t>MSW10BBA10GS101:UNIT 1 SWITCHGEAR 6.6KV INCOMING PANEL (MV UAT 2 CB9)</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -15241,12 +15336,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>WO-100826-0042</t>
+          <t>WO-100826-0043</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>CLEANING</t>
+          <t>MSW10BBA10GS102:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 1 PA FAN 1</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15274,12 +15369,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS101:UNIT 1 SWITCHGEAR 6.6KV INCOMING PANEL (MV UAT 2 CB9)</t>
+          <t>MSW10BBA10GS103:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 2 PA FAN 2</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -15302,7 +15397,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS102:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 1 PA FAN 1</t>
+          <t>MSW10BBA10GS104:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 3 SA FAN 1</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -15330,7 +15425,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS103:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 2 PA FAN 2</t>
+          <t>MSW10BBA10GS105:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 4 SA FAN 2</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -15358,7 +15453,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS104:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 3 SA FAN 1</t>
+          <t>MSW10BBA10GS106:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 5 ID FAN 1</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -15386,12 +15481,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS105:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 4 SA FAN 2</t>
+          <t>MSW10BBA10GS107:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 6 ID FAN 2</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -15414,7 +15509,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS106:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 5 ID FAN 1</t>
+          <t>MSW10BBA10GS108:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 8 BF PUMP 1</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -15442,12 +15537,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS107:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 6 ID FAN 2</t>
+          <t>MSW10BBA10GS109:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 9 BF PUMP 2</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -15470,7 +15565,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS108:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 8 BF PUMP 1</t>
+          <t>MSW10BBA10GS110:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 7 CW PUMP 3</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -15498,7 +15593,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS109:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 9 BF PUMP 2</t>
+          <t>MSW10BBA10GS111:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 11 CW PUMP 4</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -15526,7 +15621,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS110:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 7 CW PUMP 3</t>
+          <t>MSW10BBA10GS112:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 12 CW PUMP 5</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -15554,7 +15649,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS111:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 11 CW PUMP 4</t>
+          <t>MSW10BBA10GS113:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 TRAFO FEEDER</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -15582,7 +15677,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS112:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 12 CW PUMP 5</t>
+          <t>UNIT 1 SWITCHGEAR 6,6KV UNIT 1 ADAPTER</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -15610,12 +15705,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS113:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 TRAFO FEEDER</t>
+          <t>MSW10BBA10GS114:UNIT 1 SWITCHGEAR 6,6KV METERING (L10)</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -15633,22 +15728,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>WO-100826-0043</t>
+          <t>WO-100826-0044</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>UNIT 1 SWITCHGEAR 6,6KV UNIT 1 ADAPTER</t>
+          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 1</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E390" t="b">
@@ -15661,22 +15756,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>WO-100826-0043</t>
+          <t>WO-100826-0044</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>MSW10BBA10GS114:UNIT 1 SWITCHGEAR 6,6KV METERING (L10)</t>
+          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 2</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E391" t="b">
@@ -15694,7 +15789,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 1</t>
+          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 3</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -15722,7 +15817,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 2</t>
+          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 4</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -15750,7 +15845,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 3</t>
+          <t>SWITCHGEAR 6,6KV UNIT 1 OUTGOING TRAFO 1</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -15778,7 +15873,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>SWITCHGEAR 6,6KV UNIT 1 INCOMMING GENERATOR 4</t>
+          <t>SWITCHGEAR 6,6KV UNIT 1 OUTGOING TRAFO 2</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -15806,7 +15901,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SWITCHGEAR 6,6KV UNIT 1 OUTGOING TRAFO 1</t>
+          <t>MSW00BBA10CE201:MV COMMON METERING</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -15834,7 +15929,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SWITCHGEAR 6,6KV UNIT 1 OUTGOING TRAFO 2</t>
+          <t>MSW00BBA10GH201:SWITCHGEAR 6.6KV COMMON BUSTIE RIGHT</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -15862,7 +15957,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>MSW00BBA10CE201:MV COMMON METERING</t>
+          <t>MSW00BBA10GH202:SWITCHGEAR 6.6KV COMMON BUSTIE LEFT</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -15890,7 +15985,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>MSW00BBA10GH201:SWITCHGEAR 6.6KV COMMON BUSTIE RIGHT</t>
+          <t>MSW00BBA10GH203:SWITCHGEAR 6.6KV COMMON TRAFO FEEDER</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -15913,22 +16008,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>WO-100826-0044</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>MSW00BBA10GH202:SWITCHGEAR 6.6KV COMMON BUSTIE LEFT</t>
+          <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP001)</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="E400" t="b">
@@ -15941,22 +16036,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>WO-100826-0044</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>MSW00BBA10GH203:SWITCHGEAR 6.6KV COMMON TRAFO FEEDER</t>
+          <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP002)</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="E401" t="b">
@@ -15974,7 +16069,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP001)</t>
+          <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP003)</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -16002,12 +16097,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP002)</t>
+          <t>ACTUATOR TURBINE EXTRACTION III TO DEAERATOR CV 10LBD20AA210</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -16030,12 +16125,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP003)</t>
+          <t>ACTUATOR MOV PREHEATING 1 TURBINE</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -16058,12 +16153,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ACTUATOR TURBINE EXTRACTION III TO DEAERATOR CV 10LBD20AA210</t>
+          <t>ACTUATOR MOV PREHEATING 2 TURBINE</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -16086,7 +16181,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV TURBINE STOP VALVE UNIT 1</t>
+          <t>TURBINE EXTRACTION II TO LPH2 TEMPERATURE TRANSMITTER (20LBD30CT001)</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -16095,7 +16195,7 @@
         </is>
       </c>
       <c r="E406" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -16109,12 +16209,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV PREHEATING 1 TURBINE</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>TURBINE EXTRACTION III TO DEAERATOR TEMPERATURE TRANSMITTER (20LBD20CT001)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -16123,7 +16218,7 @@
         </is>
       </c>
       <c r="E407" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -16137,12 +16232,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV PREHEATING 2 TURBINE</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>TURBINE EXTRACTION I TO LPH1 TEMPERATURE TRANSMITTER (20LBD10CT001)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -16151,7 +16241,7 @@
         </is>
       </c>
       <c r="E408" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -16165,12 +16255,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION II TO LPH2 TEMPERATURE TRANSMITTER (20LBD30CT001)</t>
+          <t>MSW10MAA10CP302 : UNIT 1 TURBINE BEHIND CONTROL STAGE PRESSURE TRANSMITTER (20MAA10CP001)</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -16193,7 +16283,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION III TO DEAERATOR TEMPERATURE TRANSMITTER (20LBD20CT001)</t>
+          <t>MSW10MAA10CP303 : UNIT 1 TURBINE EXHAUST PRESSURE TRANSMITTER (20MAA10CP002)</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -16202,7 +16297,7 @@
         </is>
       </c>
       <c r="E410" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -16216,7 +16311,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION I TO LPH1 TEMPERATURE TRANSMITTER (20LBD10CT001)</t>
+          <t>MSW10MAA10CP304 : UNIT 1 TURBINE EXHAUST PRESSURE TRANSMITTER (20MAA10CP003)</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -16225,7 +16325,7 @@
         </is>
       </c>
       <c r="E411" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -16239,7 +16339,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>MSW10MAA10CP302 : UNIT 1 TURBINE BEHIND CONTROL STAGE PRESSURE TRANSMITTER (20MAA10CP001)</t>
+          <t>MSW10MAA10CP305 : UNIT 1 TURBINE EXHAUST PRESSURE TRANSMITTER (20MAA10CP004)</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -16267,7 +16367,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>MSW10MAA10CP303 : UNIT 1 TURBINE EXHAUST PRESSURE TRANSMITTER (20MAA10CP002)</t>
+          <t>MSW10MAA10CP306 : UNIT 1 TURBINE BEHIND CONTROL STAGE PRESSURE TRANSMITTER (20MAA10CP005)</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -16295,12 +16395,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MSW10MAA10CP304 : UNIT 1 TURBINE EXHAUST PRESSURE TRANSMITTER (20MAA10CP003)</t>
+          <t>MOV TURBINE STEAM EXTRACTION-1</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -16323,12 +16423,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MSW10MAA10CP305 : UNIT 1 TURBINE EXHAUST PRESSURE TRANSMITTER (20MAA10CP004)</t>
+          <t>MOV TURBINE STEAM EXTRACTION-2</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -16351,7 +16451,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>MSW10MAA10CP306 : UNIT 1 TURBINE BEHIND CONTROL STAGE PRESSURE TRANSMITTER (20MAA10CP005)</t>
+          <t>TURBINE CASING TEMPERATURE - INSIDE TRANSMITTER 10MAA10CT012</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -16379,12 +16479,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>MOV TURBINE STEAM EXTRACTION-1</t>
+          <t>TURBINE CASING TEMPERATURE - CENTER TRANSMITTER 10MAA10CT013</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -16407,12 +16507,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>MOV TURBINE STEAM EXTRACTION-2</t>
+          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT002</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -16435,12 +16535,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>TURBINE CASING TEMPERATURE - INSIDE TRANSMITTER 10MAA10CT012</t>
+          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT001</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -16463,12 +16563,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>TURBINE CASING TEMPERATURE - CENTER TRANSMITTER 10MAA10CT013</t>
+          <t>DEAERATOR PRDS TO OUTLET EXTRACTION TRANSMITTER 10LBD11CP001</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -16491,7 +16591,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT002</t>
+          <t>DEAERATOR PRDS TO OUTLET EXTRACTION II TRANSMITTER 10LBD11CP002</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -16500,7 +16605,7 @@
         </is>
       </c>
       <c r="E421" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -16514,7 +16619,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT001</t>
+          <t>FEEDWATER STORAGE TANK PRESSURE TRANSMITTER 10LAA20CP001</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -16523,7 +16633,7 @@
         </is>
       </c>
       <c r="E422" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -16537,12 +16647,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS TO OUTLET EXTRACTION TRANSMITTER 10LBD11CP001</t>
+          <t>CONTROL VALVE LPH-1</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -16565,12 +16675,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS TO OUTLET EXTRACTION II TRANSMITTER 10LBD11CP002</t>
+          <t>CONTROL VALVE LPH-2</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -16593,12 +16703,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>FEEDWATER STORAGE TANK PRESSURE TRANSMITTER 10LAA20CP001</t>
+          <t>LP HEATER 2 TRANSMITTER 10LCC40CL001</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -16621,12 +16731,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>CONTROL VALVE LPH-1</t>
+          <t>LP HEATER 2 TRANSMITTER 10LCC40CL002</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -16649,12 +16759,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>CONTROL VALVE LPH-2</t>
+          <t>LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP TRANSMITTER 10LCC20CT001</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -16677,12 +16787,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>LP HEATER 2 TRANSMITTER 10LCC40CL001</t>
+          <t>FEEDWATER STORAGE TANK TRANSMITTER 10LAA20CT001</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -16705,12 +16815,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>LP HEATER 2 TRANSMITTER 10LCC40CL002</t>
+          <t>CYCLE MAKE UP PUMP DEAERATOR TRANSMITTER 10HGC20CF001</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -16733,12 +16843,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP TRANSMITTER 10LCC20CT001</t>
+          <t>DEAERATOR TANK LEVEL 1 TRANSMITTER 10LAA20CL001</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -16761,7 +16871,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>FEEDWATER STORAGE TANK TRANSMITTER 10LAA20CT001</t>
+          <t>DEAERATOR TANK LEVEL 2 TRANSMITTER 10LAA20CL002</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -16770,7 +16885,7 @@
         </is>
       </c>
       <c r="E431" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -16784,7 +16899,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>CYCLE MAKE UP PUMP DEAERATOR TRANSMITTER 10HGC20CF001</t>
+          <t>DEAERATOR TANK LEVEL 3 TRANSMITTER 10LAA20CL003</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -16812,12 +16927,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>DEAERATOR TANK LEVEL 1 TRANSMITTER 10LAA20CL001</t>
+          <t>TURBINE EXTRACTION III TO DEAERATOR PRESSURE TRANSMITTER 10LBD20CP001</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -16840,12 +16955,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>DEAERATOR TANK LEVEL 2 TRANSMITTER 10LAA20CL002</t>
+          <t>TURBINE EXTRACTION III TO LPH PRESSURE TRANSMITTER 10LBD30CP001</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -16868,12 +16983,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>DEAERATOR TANK LEVEL 3 TRANSMITTER 10LAA20CL003</t>
+          <t>TURBINE EXTRACTION 1 TO PNEUMATIC OPERATED VALVE PRESSURE TRANSMITTER 10LBS10CP001</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -16896,12 +17011,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION III TO DEAERATOR PRESSURE TRANSMITTER 10LBD20CP001</t>
+          <t>LP HEATER 1 TRANSMITTER 10LCC30CL001</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -16924,12 +17039,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION III TO LPH PRESSURE TRANSMITTER 10LBD30CP001</t>
+          <t>LP HEATER 1 TRANSMITTER 10LCC30CL002</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -16952,12 +17067,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION 1 TO PNEUMATIC OPERATED VALVE PRESSURE TRANSMITTER 10LBS10CP001</t>
+          <t>FLOW CONDESATE TO LP HEATER 1 TRANSMITTER 10LCA40CF001</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -16980,12 +17095,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>LP HEATER 1 TRANSMITTER 10LCC30CL001</t>
+          <t>CONDENSATE TO LP HEATER TRANSMITTER 10LCA40CF001</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -17003,22 +17118,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0046</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>LP HEATER 1 TRANSMITTER 10LCC30CL002</t>
+          <t>MSW00CYE10GH101 : ALARM SYSTEM ADMIN BUILDING</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E440" t="b">
@@ -17031,22 +17146,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0046</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>FLOW CONDESATE TO LP HEATER 1 TRANSMITTER 10LCA40CF001</t>
+          <t>MSW00CYE10GH102 : ALARM SYSTEM DG SHEET</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E441" t="b">
@@ -17059,22 +17174,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0046</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>CONDENSATE TO LP HEATER TRANSMITTER 10LCA40CF001</t>
+          <t>MSW00CYE10GH103 : PANEL MAIN FIRE ALARM SYSTEM</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E442" t="b">
@@ -17092,7 +17207,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH101 : ALARM SYSTEM ADMIN BUILDING</t>
+          <t>MSW00CYE10GH104 : ALARM SYSTEM DM MCC ROOM</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -17120,12 +17235,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH102 : ALARM SYSTEM DG SHEET</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
+          <t>MSW00CYE10GH105 : ALARM SYSTEM CHP MCC</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -17134,7 +17244,7 @@
         </is>
       </c>
       <c r="E444" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -17148,12 +17258,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH103 : PANEL MAIN FIRE ALARM SYSTEM</t>
+          <t>MSW00CYE10GH106 : ALARM SYSTEM AHP MCC</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -17176,7 +17286,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH104 : ALARM SYSTEM DM MCC ROOM</t>
+          <t>MSW00CYE10GH107 : ALARM SYSTEM COOLING WATER</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -17204,7 +17314,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH105 : ALARM SYSTEM CHP MCC</t>
+          <t>MSW00CYE10GH108 : ALARM SYSTEM DM/RW.FW TW PUMP</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -17213,7 +17328,7 @@
         </is>
       </c>
       <c r="E447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -17227,7 +17342,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH106 : ALARM SYSTEM AHP MCC</t>
+          <t>MSW00CYE10GH109 : ALARM SYSTEM WORKSHOP OFFICE ROOM</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -17236,7 +17356,7 @@
         </is>
       </c>
       <c r="E448" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -17250,7 +17370,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH107 : ALARM SYSTEM COOLING WATER</t>
+          <t>MSW00CYE10GH110 : ALARM SYSTEM SWAS ROOM</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -17278,7 +17398,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH108 : ALARM SYSTEM DM/RW.FW TW PUMP</t>
+          <t>MSW00CYE10GH111 : ALARM SYSTEM STG BUILDING</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -17306,7 +17426,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH109 : ALARM SYSTEM WORKSHOP OFFICE ROOM</t>
+          <t>MSW00CYE10GH113 : ALARM SYSTEM SWITCHYARD BUILDING</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -17334,7 +17454,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH110 : ALARM SYSTEM SWAS ROOM</t>
+          <t>MSW00CYE10GH114 : ALARM SYSTEM REMOTE SUBSTATION BUILDING</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -17357,22 +17477,22 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>WO-100826-0046</t>
+          <t>WO-100826-0047</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH111 : ALARM SYSTEM STG BUILDING</t>
+          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E453" t="b">
@@ -17385,22 +17505,22 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>WO-100826-0046</t>
+          <t>WO-100826-0047</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH113 : ALARM SYSTEM SWITCHYARD BUILDING</t>
+          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF001</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E454" t="b">
@@ -17413,22 +17533,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>WO-100826-0046</t>
+          <t>WO-100826-0047</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH114 : ALARM SYSTEM REMOTE SUBSTATION BUILDING</t>
+          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF002</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E455" t="b">
@@ -17446,12 +17566,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
+          <t>P.A APH OUTLET PRESSURE TRANSMITTER 10HLA15CP001</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -17469,17 +17589,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>WO-100826-0047</t>
+          <t>WO-100826-0048</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF001</t>
+          <t>AIR SUB1 FLOW DP TRANSMITTER 10HJL10CF010</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -17497,17 +17617,17 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>WO-100826-0047</t>
+          <t>WO-100826-0048</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF002</t>
+          <t>AIR SUB2 FLOW DP TRANSMITTER 10HJL11CF010</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -17525,17 +17645,17 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>WO-100826-0047</t>
+          <t>WO-100826-0048</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>P.A APH OUTLET PRESSURE TRANSMITTER 10HLA15CP001</t>
+          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF001</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -17558,12 +17678,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>AIR SUB1 FLOW DP TRANSMITTER 10HJL10CF010</t>
+          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF002</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -17586,7 +17706,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>AIR SUB2 FLOW DP TRANSMITTER 10HJL11CF010</t>
+          <t>SA APH OUTLET PRESSURE TRANSMITTER 10HLA25CP001</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -17614,12 +17734,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF001</t>
+          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 1 20HJL10AA010</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -17642,12 +17762,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF002</t>
+          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 2 20HJL11AA010</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -17670,12 +17790,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>SA APH OUTLET PRESSURE TRANSMITTER 10HLA25CP001</t>
+          <t>UNIT 1 SECONDARY AIR FAN IGV SA CONTROL DAMPER 20HLA25AA010</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -17693,22 +17813,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>WO-100826-0048</t>
+          <t>WO-100826-0049</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 1 20HJL10AA010</t>
+          <t>PM PC OWS</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E465" t="b">
@@ -17721,22 +17841,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>WO-100826-0048</t>
+          <t>WO-100826-0049</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 2 20HJL11AA010</t>
+          <t>PM PC EWS</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E466" t="b">
@@ -17749,26 +17869,21 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>WO-100826-0048</t>
+          <t>WO-100826-0049</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>UNIT 1 SECONDARY AIR FAN IGV SA CONTROL DAMPER 20HLA25AA010</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
+          <t>PM panel RIO</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E467" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -17777,17 +17892,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>WO-100826-0049</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>PM PC OWS</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM VENTING ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -17805,17 +17920,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>WO-100826-0049</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>PM PC EWS</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV VENTING REGULATING VALVE</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -17833,12 +17948,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>WO-100826-0049</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>PM panel RIO</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM CBD ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -17847,7 +17967,7 @@
         </is>
       </c>
       <c r="E470" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -17861,12 +17981,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM VENTING ISOLATION VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV CBD REGULATING VALVE</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -17889,12 +18009,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV VENTING REGULATING VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM IBD ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -17917,12 +18037,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM CBD ISOLATION VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV IBD REGULATING VALVE</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -17945,12 +18065,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV CBD REGULATING VALVE</t>
+          <t>DRUM LEVEL TRANSMITTER 10HAD10CL001</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -17973,12 +18093,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM IBD ISOLATION VALVE</t>
+          <t>DRUM LEVEL TRANSMITTER 10HAD10CL002</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -18001,12 +18121,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV IBD REGULATING VALVE</t>
+          <t>DRUM LEVEL TRANSMITTER 10HAD10CL003</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -18029,7 +18149,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>DRUM LEVEL TRANSMITTER 10HAD10CL001</t>
+          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP002</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -18057,7 +18177,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>DRUM LEVEL TRANSMITTER 10HAD10CL002</t>
+          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP003</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -18085,7 +18205,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>DRUM LEVEL TRANSMITTER 10HAD10CL003</t>
+          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP001</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -18108,22 +18228,22 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP002</t>
+          <t>COMBUSTER ASH DRAIN 1 (BED ASH COOLER DRAIN) MOV 10HHC01AA001</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="E480" t="b">
@@ -18136,22 +18256,22 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP003</t>
+          <t>COMBUSTER ASH DRAIN 2 (EMERGENCY ASH DRAIN) MOV 10HHC01AA002</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="E481" t="b">
@@ -18164,22 +18284,22 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP001</t>
+          <t>LIMESTONE GATE VALVE</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="E482" t="b">
@@ -18197,7 +18317,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>COMBUSTER ASH DRAIN 1 (BED ASH COOLER DRAIN) MOV 10HHC01AA001</t>
+          <t>ACTUATOR BED MATERIAL DISCHARGE GATE VALVE 10ETG31AA01</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -18225,7 +18345,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>COMBUSTER ASH DRAIN 2 (EMERGENCY ASH DRAIN) MOV 10HHC01AA002</t>
+          <t>COMBUSTOR LOWER PRESSURE TRANSMITTER 10HHC01CP001</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -18253,12 +18373,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>LIMESTONE GATE VALVE</t>
+          <t>MSW10HHC10CP102 : UNIT 1 COMBUSTOR DP WITH GRATE 10HHC01CP011</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -18281,12 +18401,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>ACTUATOR BED MATERIAL DISCHARGE GATE VALVE 10ETG31AA01</t>
+          <t>MSW10HHC10CP103 : UNIT 1 COMBUSTOR UPPER DP 10HHC01CP012</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -18309,12 +18429,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>COMBUSTOR LOWER PRESSURE TRANSMITTER 10HHC01CP001</t>
+          <t>AIR COMBUSTOR AT LEVEL PRES TRANSMITTER 10HHC01CP060</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -18337,12 +18457,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>MSW10HHC10CP102 : UNIT 1 COMBUSTOR DP WITH GRATE 10HHC01CP011</t>
+          <t>MSW10HHC10CT101 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT011</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -18365,12 +18485,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MSW10HHC10CP103 : UNIT 1 COMBUSTOR UPPER DP 10HHC01CP012</t>
+          <t>MSW10HHC10CT102 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT012</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -18393,12 +18513,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>AIR COMBUSTOR AT LEVEL PRES TRANSMITTER 10HHC01CP060</t>
+          <t>MSW10HHC10CT103 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT013</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -18421,7 +18541,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MSW10HHC10CT101 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT011</t>
+          <t>MSW10HHC10CT104 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT041</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -18430,7 +18555,7 @@
         </is>
       </c>
       <c r="E491" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -18444,7 +18569,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MSW10HHC10CT102 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT012</t>
+          <t>MSW10HHC10CT105 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT042</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -18453,7 +18583,7 @@
         </is>
       </c>
       <c r="E492" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -18467,7 +18597,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MSW10HHC10CT103 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT013</t>
+          <t>MSW10HHC10CT106 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT043</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -18476,7 +18611,7 @@
         </is>
       </c>
       <c r="E493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -18490,7 +18625,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MSW10HHC10CT104 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT041</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP003</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -18499,7 +18639,7 @@
         </is>
       </c>
       <c r="E494" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -18513,7 +18653,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MSW10HHC10CT105 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT042</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP002</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -18522,7 +18667,7 @@
         </is>
       </c>
       <c r="E495" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -18536,7 +18681,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MSW10HHC10CT106 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT043</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP001</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -18545,7 +18695,7 @@
         </is>
       </c>
       <c r="E496" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -18559,7 +18709,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP003</t>
+          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER 10HBK01CP030</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -18587,12 +18737,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP002</t>
+          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER 10HBK01CP050</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -18610,17 +18760,17 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP001</t>
+          <t>CYCLONE TO SEALPOT PRESSURE TRANSMITTER 10HDF01CP001</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -18638,22 +18788,22 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0053</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER 10HBK01CP030</t>
+          <t>ACTUATOR DAMPER SEALPOT BLOWER 1</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E500" t="b">
@@ -18666,22 +18816,22 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0053</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER 10HBK01CP050</t>
+          <t>ACTUATOR DAMPER SEALPOT BLOWER 2</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E501" t="b">
@@ -18694,22 +18844,22 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0053</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MSW10HDF10CP102 : UNIT 1 BACKPASS INLET PRESSURE</t>
+          <t>CALIBRATION PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E502" t="b">
@@ -18722,12 +18872,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>CYCLONE TO SEALPOT PRESSURE TRANSMITTER 10HDF01CP001</t>
+          <t>ERV PRESSURE SWITCH 10LBA20CP502</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -18737,7 +18887,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E503" t="b">
@@ -18750,21 +18900,26 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>MSW10HDF10CT101 : UNIT 1 BACKPASS INLET TEMPERATURE</t>
+          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT001</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E504" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -18773,21 +18928,26 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>MSW10HDF10CT102 : UNIT 1 CYCLONE OUTLET TEMP 10HNA01CT001</t>
+          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT002</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E505" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -18796,21 +18956,26 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>MSW10HDF10CT103 : UNIT 1 BACKPASS INLET TEMPERATURE</t>
+          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT003</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E506" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -18819,21 +18984,26 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>MSW10HDF10CT104 : UNIT 1 CYCLONE INLET TEMPERATURE</t>
+          <t>ACTUATOR MAIN STEAM LINE (START UP BYPASS) TO DEAERATOR PRDS I/L CV 10LBH10AA210</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E507" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -18842,17 +19012,17 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>WO-100826-0053</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>ACTUATOR DAMPER SEALPOT BLOWER 1</t>
+          <t>MS START-UP VENT VALVE (REGULATING) MOV 10LBA21AA011</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -18870,17 +19040,17 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>WO-100826-0053</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>ACTUATOR DAMPER SEALPOT BLOWER 2</t>
+          <t>MS START-UP VENT VALVE (ISOLATION) MOV 10LBA21AA001</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -18898,17 +19068,17 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>WO-100826-0053</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>CALIBRATION PRESSURE TRANSMITTER</t>
+          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP001</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -18926,12 +19096,17 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>WO-100826-0053</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>CALIBRATION TEMPERATURE TRANSMITTER</t>
+          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP002</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -18940,7 +19115,7 @@
         </is>
       </c>
       <c r="E511" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -18954,12 +19129,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>ERV PRESSURE SWITCH 10LBA20CP502</t>
+          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP003</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -18982,7 +19157,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT001</t>
+          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF001</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -18991,7 +19171,7 @@
         </is>
       </c>
       <c r="E513" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -19005,7 +19185,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT002</t>
+          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF002</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -19014,7 +19199,7 @@
         </is>
       </c>
       <c r="E514" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -19023,21 +19208,26 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0055</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT003</t>
+          <t>MSW10MAV10-M101 : UNIT 1 JACKING OIL PUMP MOTOR</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E515" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -19046,22 +19236,22 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0055</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>ACTUATOR MAIN STEAM LINE (START UP BYPASS) TO DEAERATOR PRDS I/L CV 10LBH10AA210</t>
+          <t>MSW10MAV10CP101 : UNIT 1 JACKING OIL PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E516" t="b">
@@ -19074,22 +19264,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0056</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>MS START-UP VENT VALVE (REGULATING) MOV 10LBA21AA011</t>
+          <t>INSPEKSI &amp; PM OIL PUMP MOTOR ( AUXILIARY, EMERGENCY, JACKING, BREATHER )</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E517" t="b">
@@ -19102,22 +19292,22 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0056</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>MS START-UP VENT VALVE (ISOLATION) MOV 10LBA21AA001</t>
+          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 10MAV40CP001</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E518" t="b">
@@ -19130,22 +19320,22 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0056</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP001</t>
+          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 10MAV40CP002</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E519" t="b">
@@ -19158,22 +19348,22 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0056</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP002</t>
+          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 10MAV40CP003</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E520" t="b">
@@ -19186,22 +19376,22 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP003</t>
+          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP001)</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E521" t="b">
@@ -19214,22 +19404,22 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF001</t>
+          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP002)</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E522" t="b">
@@ -19242,22 +19432,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF002</t>
+          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP003)</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E523" t="b">
@@ -19270,22 +19460,22 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>WO-100826-0055</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MSW10MAV10-M101 : UNIT 1 JACKING OIL PUMP MOTOR</t>
+          <t>VALVE BLOCK - OUTLET POSITION LIVE STEAM PT (20MAX45CP004)</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E524" t="b">
@@ -19298,22 +19488,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>WO-100826-0055</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MSW10MAV10CP101 : UNIT 1 JACKING OIL PRESSURE TRANSMITTER</t>
+          <t>CONTROL OIL PRESSURE PT (20MAX40CP001)</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E525" t="b">
@@ -19326,12 +19516,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>WO-100826-0056</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>INSPEKSI &amp; PM OIL PUMP MOTOR ( AUXILIARY, EMERGENCY, JACKING, BREATHER )</t>
+          <t>VALVE CHEST TEMPERATURE TRANSMITTER 10MAA10CT011</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -19349,17 +19539,17 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>WO-100826-0056</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 10MAV40CP001</t>
+          <t>LIVE STEAM PRESSURE TRANSMITTER 10LBA10CP001</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -19377,22 +19567,22 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>WO-100826-0056</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 10MAV40CP002</t>
+          <t>CALIBRATION/FUNCTION TEST HP BYPASS CONTROL VALVE 20LBF10AA210</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E528" t="b">
@@ -19405,26 +19595,21 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>WO-100826-0056</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 10MAV40CP003</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
+          <t>HP BYPASS TEMPERATURE TRANSMITTER 10LBF10CT001</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E529" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -19433,17 +19618,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP001)</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
+          <t>BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -19452,7 +19632,7 @@
         </is>
       </c>
       <c r="E530" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -19461,17 +19641,17 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP002)</t>
+          <t>MSW10LBF10CG101 : UNIT 1 STEAM BYPASS REDUCING CONTROL VALVE PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -19489,12 +19669,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP003)</t>
+          <t>MSW10LBF10CP101 : UNIT 1 STEAM BYPASS REDUCING PRESSURE TRANSMITTER 10LBF10CP001</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -19517,26 +19697,21 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>VALVE BLOCK - OUTLET POSITION LIVE STEAM PT (20MAX45CP004)</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
+          <t>MSW10LBF10CT101 : UNIT 1 STEAM BYPASS REDUCING TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E533" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -19545,22 +19720,22 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>CONTROL OIL PRESSURE PT (20MAX40CP001)</t>
+          <t>DRAIN OF ESV 10MAL10AA210</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E534" t="b">
@@ -19573,21 +19748,26 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>VALVE CHEST TEMPERATURE TRANSMITTER 10MAA10CT011</t>
+          <t>DRAIN OF CV CHAMBER 10MAL20AA210</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E535" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -19596,26 +19776,21 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>LIVE STEAM PRESSURE TRANSMITTER 10LBA10CP001</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
+          <t>TURBINE DRAIN VALVE AFTER FIRST STAGE 10MAL30AA210</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -19624,26 +19799,21 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>CALIBRATION/FUNCTION TEST HP BYPASS CONTROL VALVE 20LBF10AA210</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>TURBINE DRAIN VALVE 10MAL40AA210</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E537" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -19652,17 +19822,17 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>HP BYPASS TEMPERATURE TRANSMITTER 10LBF10CT001</t>
+          <t>TURBINE DRAIN VALVE 10MAL50AA210</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E538" t="b">
@@ -19675,17 +19845,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
+          <t>TURBINE DRAIN VALVE 10MAL60AA210</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E539" t="b">
@@ -19698,26 +19868,21 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MSW10LBF10CG101 : UNIT 1 STEAM BYPASS REDUCING CONTROL VALVE PRESSURE TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>TURBINE DRAIN VALVE 10MAL70AA210</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E540" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -19726,17 +19891,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0060</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MSW10LBF10CP101 : UNIT 1 STEAM BYPASS REDUCING PRESSURE TRANSMITTER 10LBF10CP001</t>
+          <t>MSW10MAJ10-M102 : UNIT 1 VACUUM PUMP A MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, And SISTEM COOLING MOTOR)</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -19754,12 +19919,17 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0060</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MSW10LBF10CT101 : UNIT 1 STEAM BYPASS REDUCING TEMPERATURE TRANSMITTER</t>
+          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-1</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -19768,7 +19938,7 @@
         </is>
       </c>
       <c r="E542" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -19777,22 +19947,22 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0060</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>DRAIN OF ESV 10MAL10AA210</t>
+          <t>MSW10MAJ10AA101 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E543" t="b">
@@ -19805,17 +19975,17 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0060</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>DRAIN OF CV CHAMBER 10MAL20AA210</t>
+          <t>MSW10MAJ10CG101 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -19833,21 +20003,26 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0061</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE AFTER FIRST STAGE 10MAL30AA210</t>
+          <t>MSW10MAJ10-M202 : UNIT 1 VACUUM PUMP B MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, And SISTEM COOLING MOTOR)</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E545" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -19856,21 +20031,26 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0061</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL40AA210</t>
+          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-2</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E546" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -19879,21 +20059,26 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0061</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL50AA210</t>
+          <t>MSW10MAJ10AA201 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E547" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -19902,12 +20087,17 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0061</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL60AA210</t>
+          <t>MSW10MAJ10CG201 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -19916,7 +20106,7 @@
         </is>
       </c>
       <c r="E548" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -19925,21 +20115,26 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0062</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL70AA210</t>
+          <t>MSW10MAG10CP103 : UNIT 1 CONDENSER BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E549" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -19948,17 +20143,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>WO-100826-0060</t>
+          <t>WO-100826-0062</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>MSW10MAJ10-M102 : UNIT 1 VACUUM PUMP A MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, And SISTEM COOLING MOTOR)</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB11CT001</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -19967,7 +20157,7 @@
         </is>
       </c>
       <c r="E550" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -19976,26 +20166,21 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>WO-100826-0060</t>
+          <t>WO-100826-0062</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-1</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB12CT001</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E551" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -20004,26 +20189,21 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>WO-100826-0060</t>
+          <t>WO-100826-0062</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>MSW10MAJ10AA101 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB21CT001</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E552" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -20032,26 +20212,21 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>WO-100826-0060</t>
+          <t>WO-100826-0062</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>MSW10MAJ10CG101 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB22CT001</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E553" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -20060,12 +20235,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>WO-100826-0061</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>MSW10MAJ10-M202 : UNIT 1 VACUUM PUMP B MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, And SISTEM COOLING MOTOR)</t>
+          <t>INSPECTION FRAME MOTOR</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -20088,12 +20263,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>WO-100826-0061</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-2</t>
+          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -20103,7 +20278,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E555" t="b">
@@ -20116,12 +20291,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>WO-100826-0061</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>MSW10MAJ10AA201 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -20131,7 +20306,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E556" t="b">
@@ -20144,12 +20319,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>WO-100826-0061</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>MSW10MAJ10CG201 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
+          <t>INSPECTION COOLING FAN</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -20159,7 +20334,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E557" t="b">
@@ -20172,17 +20347,17 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>WO-100826-0062</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>MSW10MAG10CP103 : UNIT 1 CONDENSER BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -20200,12 +20375,17 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>WO-100826-0062</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB11CT001</t>
+          <t>INSPECTION TERMINASI</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -20214,7 +20394,7 @@
         </is>
       </c>
       <c r="E559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -20223,12 +20403,17 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>WO-100826-0062</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB12CT001</t>
+          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -20237,7 +20422,7 @@
         </is>
       </c>
       <c r="E560" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -20246,12 +20431,17 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>WO-100826-0062</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB21CT001</t>
+          <t>CALIBRATION LIMIT SWITCH</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -20260,7 +20450,7 @@
         </is>
       </c>
       <c r="E561" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -20269,12 +20459,17 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>WO-100826-0062</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB22CT001</t>
+          <t>PRESSURE TRANSMITTER CONDENSATE PUMP TO DELIVERY 10LCA30CP001</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -20283,7 +20478,7 @@
         </is>
       </c>
       <c r="E562" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -20297,17 +20492,17 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>INSPECTION FRAME MOTOR</t>
+          <t>ACTUATOR CONDENSATE PUMP RECIRCULATION CONTROL VALVE 10LCA31AA210</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E563" t="b">
@@ -20325,17 +20520,17 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
+          <t>ACTUATOR MAIN CONDENSATE CONTROL VALVE 10LCA30AA240</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E564" t="b">
@@ -20353,17 +20548,17 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>INSULATION RESISTANCE INSPECTION</t>
+          <t>CEP DISCHARGE ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E565" t="b">
@@ -20376,12 +20571,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>INSPECTION COOLING FAN</t>
+          <t>INSPECTION FRAME MOTOR</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -20404,17 +20599,17 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>WINDING RESISTANCE INSPECTION</t>
+          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -20432,17 +20627,17 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>INSPECTION TERMINASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -20460,17 +20655,17 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
+          <t>INSPECTION COOLING FAN</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -20488,12 +20683,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>CALIBRATION LIMIT SWITCH</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -20516,17 +20711,17 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>PRESSURE TRANSMITTER CONDENSATE PUMP TO DELIVERY 10LCA30CP001</t>
+          <t>INSPECTION TERMINASI</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -20544,12 +20739,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>ACTUATOR CONDENSATE PUMP RECIRCULATION CONTROL VALVE 10LCA31AA210</t>
+          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -20559,7 +20754,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E572" t="b">
@@ -20572,12 +20767,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>ACTUATOR MAIN CONDENSATE CONTROL VALVE 10LCA30AA240</t>
+          <t>CALIBRATION LIMIT SWITCH</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -20587,7 +20782,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E573" t="b">
@@ -20600,7 +20795,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -20628,22 +20823,22 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>INSPECTION FRAME MOTOR</t>
+          <t>FREQUENCY PROTECTION TEST</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E575" t="b">
@@ -20656,22 +20851,22 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
+          <t>GENERATOR DIFFERENTIAL PROTECTION TEST</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E576" t="b">
@@ -20684,22 +20879,22 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>INSULATION RESISTANCE INSPECTION</t>
+          <t>SHORT CIRCUIT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E577" t="b">
@@ -20712,22 +20907,22 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>INSPECTION COOLING FAN</t>
+          <t>OVERCURRENT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E578" t="b">
@@ -20740,22 +20935,22 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>WINDING RESISTANCE INSPECTION</t>
+          <t>OVERVOLTAGE PROTECTION TEST</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E579" t="b">
@@ -20768,22 +20963,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>INSPECTION TERMINASI</t>
+          <t>ROTOR EARTH FAULT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E580" t="b">
@@ -20796,22 +20991,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
+          <t>STATOR EARTH FAULT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E581" t="b">
@@ -20824,22 +21019,22 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>CALIBRATION LIMIT SWITCH</t>
+          <t>REVERSE POWER PROTECTION TEST</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E582" t="b">
@@ -20852,17 +21047,17 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>CEP DISCHARGE ISOLATION VALVE</t>
+          <t>UNDER EXCITATION PROTECTION TEST</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -20885,12 +21080,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>FREQUENCY PROTECTION TEST</t>
+          <t>OVER EXCITATION PROTECTION TEST</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -20913,12 +21108,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>GENERATOR DIFFERENTIAL PROTECTION TEST</t>
+          <t>NEGATIVE SEQUENCE PROTECTION TEST</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -20941,12 +21136,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>SHORT CIRCUIT PROTECTION TEST</t>
+          <t>OVERLOAD PROTECTION TEST</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -20969,12 +21164,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>OVERCURRENT PROTECTION TEST</t>
+          <t>CLEANING AND TIGHTENING</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -20992,12 +21187,12 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0066</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>OVERVOLTAGE PROTECTION TEST</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE PANEL</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -21020,12 +21215,12 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0066</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>ROTOR EARTH FAULT PROTECTION TEST</t>
+          <t>MEMBERSIHKAN FILTER PANEL</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -21048,12 +21243,12 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0066</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>STATOR EARTH FAULT PROTECTION TEST</t>
+          <t>PEMELIHARAAN FAN CONVERTER UNITROL</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -21076,12 +21271,17 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0066</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>REVERSE POWER PROTECTION TEST</t>
+          <t>MEMBERSIHKAN KOMPARTEMEN DALAM PANEL</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -21090,7 +21290,7 @@
         </is>
       </c>
       <c r="E591" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -21099,12 +21299,17 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0066</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>UNDER EXCITATION PROTECTION TEST</t>
+          <t>HOUSEKEEPING</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -21113,7 +21318,7 @@
         </is>
       </c>
       <c r="E592" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -21122,21 +21327,26 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>OVER EXCITATION PROTECTION TEST</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 1</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E593" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -21145,21 +21355,26 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>NEGATIVE SEQUENCE PROTECTION TEST</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 2</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E594" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -21168,21 +21383,26 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>OVERLOAD PROTECTION TEST</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 3</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E595" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -21191,21 +21411,26 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>CLEANING AND TIGHTENING</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 4</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E596" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -21214,12 +21439,12 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>WO-100826-0066</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE PANEL</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 5</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -21229,7 +21454,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E597" t="b">
@@ -21242,12 +21467,12 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>WO-100826-0066</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>MEMBERSIHKAN FILTER PANEL</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 6</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -21257,7 +21482,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E598" t="b">
@@ -21270,12 +21495,12 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>WO-100826-0066</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>PEMELIHARAAN FAN CONVERTER UNITROL</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 7</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -21285,7 +21510,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E599" t="b">
@@ -21298,12 +21523,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>WO-100826-0066</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>MEMBERSIHKAN KOMPARTEMEN DALAM PANEL</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 8</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -21313,7 +21538,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E600" t="b">
@@ -21326,12 +21551,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>WO-100826-0066</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 9</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -21341,7 +21566,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E601" t="b">
@@ -21359,7 +21584,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 1</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 10</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -21387,7 +21612,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 2</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 11</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -21415,7 +21640,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 3</t>
+          <t>SOOT BLOWER STEAM OUTLET TRANSMITTER 10HCB10CP001</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -21443,12 +21668,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 4</t>
+          <t>SOOT BLOWER STEAM FLOW TRANSMITTER 10HCB10CF001</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -21471,17 +21696,17 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 5</t>
+          <t>ACTUATOR VALVE DRAIN SOOT BLOWER 10HCB10AA201</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E606" t="b">
@@ -21499,17 +21724,17 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 6</t>
+          <t>SOOT BLOWER VALVE MOV 10HCB10AA001</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E607" t="b">
@@ -21527,17 +21752,17 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 7</t>
+          <t>ACTUATOR SOOT BLOWER CONTROL VALVE 10HCB10EX001</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E608" t="b">
@@ -21550,22 +21775,22 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0068</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 8</t>
+          <t>PM PC OWS</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E609" t="b">
@@ -21578,22 +21803,22 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0068</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 9</t>
+          <t>PM PC EWS</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E610" t="b">
@@ -21606,26 +21831,21 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0068</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 10</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>PM panel RIO</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E611" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -21634,17 +21854,17 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 11</t>
+          <t>INSPEKSI LV TRANSFORMER</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -21662,17 +21882,17 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>SOOT BLOWER STEAM OUTLET TRANSMITTER 10HCB10CP001</t>
+          <t>RDC Test LV TRANSFORMER</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -21690,17 +21910,17 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>SOOT BLOWER STEAM FLOW TRANSMITTER 10HCB10CF001</t>
+          <t>FUNGSI RACK OUT RACK IN</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -21718,22 +21938,22 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>ACTUATOR VALVE DRAIN SOOT BLOWER 10HCB10AA201</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E615" t="b">
@@ -21746,22 +21966,22 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>SOOT BLOWER VALVE MOV 10HCB10AA001</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E616" t="b">
@@ -21774,22 +21994,22 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>ACTUATOR SOOT BLOWER CONTROL VALVE 10HCB10EX001</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST *)including busbar and busduct</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E617" t="b">
@@ -21802,21 +22022,26 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>WO-100826-0068</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>PM PC OWS</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E618" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -21825,21 +22050,26 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>WO-100826-0068</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>PM PC EWS</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E619" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -21848,21 +22078,26 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>WO-100826-0068</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>PM panel RIO</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E620" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -21876,7 +22111,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>INSPEKSI LV TRANSFORMER</t>
+          <t>PERAWATAN KOMPARTEMEN TRAFO KONTROL</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -21904,7 +22139,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>RDC Test LV TRANSFORMER</t>
+          <t>PERAWATAN KOMPARTEMEN SOOTBLOWER MCC FEEDER</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -21932,7 +22167,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>FUNGSI RACK OUT RACK IN</t>
+          <t>PERAWATAN KOMPARTEMEN TG MCC FEEDER</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -21960,7 +22195,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN ADAPTER PANEL</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -21988,7 +22223,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>BUSTIE BUSDUCT CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -22016,7 +22251,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>BUSBAR INSULATION RESISTANCE TEST *)including busbar and busduct</t>
+          <t>PERAWATAN ACB INCOMMING</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -22044,7 +22279,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>BUSBAR CONTACT RESISTANCE TEST</t>
+          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -22072,7 +22307,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>INCOMING ACB CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -22100,7 +22335,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -22128,7 +22363,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN TRAFO KONTROL</t>
+          <t>PERAWATAN ACB ESP FEEDER</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -22156,7 +22391,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN SOOTBLOWER MCC FEEDER</t>
+          <t>ESP FEEDER ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -22184,7 +22419,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN TG MCC FEEDER</t>
+          <t>ACB CONTACT RESISTANCE TEST ESP FEEDER</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -22212,7 +22447,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN ADAPTER PANEL</t>
+          <t>ESP FEEDER CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -22240,7 +22475,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>BUSTIE BUSDUCT CONTACT RESISTANCE TEST</t>
+          <t>PERAWATAN ACB BOILER FEEDER</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -22268,7 +22503,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB INCOMMING</t>
+          <t>ACB CONTACT RESISTANCE TEST BOILER FEEDER</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -22296,7 +22531,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
+          <t>BOILER FEEDER CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -22324,7 +22559,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>INCOMING ACB CONTACT RESISTANCE TEST</t>
+          <t>PERAWATAN ACB COOLING TOWER MCC FEEDER</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -22352,7 +22587,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>CB ANALYSIS TEST</t>
+          <t>COOLING TOWER FEEDER ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -22380,7 +22615,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB ESP FEEDER</t>
+          <t>ACB CONTACT RESISTANCE TEST COOLING TOWER FEEDER</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -22408,7 +22643,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>ESP FEEDER ACB INSULATION RESISTANCE TEST</t>
+          <t>COOLING TOWER FEEDER CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -22436,7 +22671,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>ACB CONTACT RESISTANCE TEST ESP FEEDER</t>
+          <t>INSPECTION HEATER BUSDUCT</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -22464,7 +22699,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>ESP FEEDER CB ANALYSIS TEST</t>
+          <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -22492,7 +22727,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB BOILER FEEDER</t>
+          <t>INSPECTION SILICA BUSDUCT</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -22520,7 +22755,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>ACB CONTACT RESISTANCE TEST BOILER FEEDER</t>
+          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -22548,7 +22783,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>BOILER FEEDER CB ANALYSIS TEST</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -22571,12 +22806,12 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB COOLING TOWER MCC FEEDER</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -22599,12 +22834,12 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>COOLING TOWER FEEDER ACB INSULATION RESISTANCE TEST</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -22627,12 +22862,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>ACB CONTACT RESISTANCE TEST COOLING TOWER FEEDER</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -22655,12 +22890,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>COOLING TOWER FEEDER CB ANALYSIS TEST</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -22683,12 +22918,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>INSPECTION HEATER BUSDUCT</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -22711,12 +22946,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
+          <t>PERAWATAN MODULE WITHDRAWABLE</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -22739,12 +22974,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>INSPECTION SILICA BUSDUCT</t>
+          <t>PERAWATAN ACB INCOMMING</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -22767,12 +23002,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -22795,12 +23030,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -22823,12 +23058,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -22851,12 +23086,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -22879,7 +23114,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -22907,7 +23142,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -22935,7 +23170,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -22963,7 +23198,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -22991,12 +23226,12 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB INCOMMING</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -23019,17 +23254,17 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -23047,17 +23282,17 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -23075,17 +23310,17 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -23103,17 +23338,17 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>BUSBAR INSULATION RESISTANCE TEST</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -23131,17 +23366,17 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>BUSBAR CONTACT RESISTANCE TEST</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -23159,17 +23394,17 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -23187,17 +23422,17 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>PERAWATAN MODULE WITHDRAWABLE</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -23215,17 +23450,17 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>PERAWATAN MODULE WITHDRAWABLE</t>
+          <t>PERAWATAN ACB INCOMMING</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -23243,17 +23478,17 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -23276,7 +23511,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>INCOMING ACB CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -23304,7 +23539,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -23332,12 +23567,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>BUSBAR INSULATION RESISTANCE TEST</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -23355,22 +23590,22 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0073</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>BUSBAR CONTACT RESISTANCE TEST</t>
+          <t>GLAND STEAM CONDENSER VENTING MOTOR</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E674" t="b">
@@ -23383,22 +23618,22 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0073</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>GLAND STEAM PRESSURE TRANSMITTER 10MAW11CP001</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E675" t="b">
@@ -23411,22 +23646,22 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0073</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>ACTUATOR GLAND STEAM PRESSURE CONTROL VALVE 10MAW10AA210</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E676" t="b">
@@ -23439,22 +23674,22 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0073</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>PERAWATAN MODULE WITHDRAWABLE</t>
+          <t>ACTUATOR GLAND STEAM TEMPERATURE CONTROL VALVE 10LCE10AA210</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E677" t="b">
@@ -23467,22 +23702,22 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0073</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB INCOMMING</t>
+          <t>GENERAL CLEANING</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E678" t="b">
@@ -23495,12 +23730,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
+          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -23510,7 +23745,7 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E679" t="b">
@@ -23523,12 +23758,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>INCOMING ACB CONTACT RESISTANCE TEST</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -23538,7 +23773,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E680" t="b">
@@ -23551,12 +23786,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>CB ANALYSIS TEST</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -23566,7 +23801,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E681" t="b">
@@ -23579,22 +23814,22 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E682" t="b">
@@ -23607,22 +23842,22 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>WO-100826-0073</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GLAND STEAM CONDENSER VENTING MOTOR</t>
+          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E683" t="b">
@@ -23635,22 +23870,22 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>WO-100826-0073</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>GLAND STEAM PRESSURE TRANSMITTER 10MAW11CP001</t>
+          <t>Panel Bapcon - Rapcon Field 1</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E684" t="b">
@@ -23663,22 +23898,22 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>WO-100826-0073</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>ACTUATOR GLAND STEAM PRESSURE CONTROL VALVE 10MAW10AA210</t>
+          <t>Panel Bapcon - Rapcon Field 2</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E685" t="b">
@@ -23691,12 +23926,12 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>WO-100826-0073</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>ACTUATOR GLAND STEAM TEMPERATURE CONTROL VALVE 10LCE10AA210</t>
+          <t>Panel Bapcon - Rapcon Field 3</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -23706,7 +23941,7 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E686" t="b">
@@ -23719,22 +23954,22 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>WO-100826-0073</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>GENERAL CLEANING</t>
+          <t>Panel Bapcon - Rapcon Field 4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E687" t="b">
@@ -23747,22 +23982,22 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
+          <t>Panel Bapcon - Rapcon Field 5</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E688" t="b">
@@ -23775,22 +24010,22 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
+          <t>Panel Bapcon - Rapcon Field 6</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E689" t="b">
@@ -23803,22 +24038,17 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
+          <t>MOV MAIN STEAM DRAIN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>FERRYUS</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E690" t="b">
@@ -23831,22 +24061,22 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
+          <t>ACTUATOR DESH-1 SPRAY WATER ISOLATION</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E691" t="b">
@@ -23859,22 +24089,22 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0039</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER</t>
+          <t>ACTUATOR DESH-2 SPRAY WATER ISOLATION</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E692" t="b">
@@ -23887,22 +24117,22 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0160</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 1</t>
+          <t>ACTUATOR INLET ID FAN 1 MOV 10HNA61AA001</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E693" t="b">
@@ -23915,22 +24145,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0160</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 2</t>
+          <t>ACTUATOR OUTLET ID FAN 1 MOV 10HNA71AA001</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E694" t="b">
@@ -23943,22 +24173,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0020</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 3</t>
+          <t>ACTUATOR MOV OUTLET PA FAN 1</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E695" t="b">
@@ -23971,22 +24201,22 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0020</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 4</t>
+          <t>ACTUATOR MOV PA FAN 1</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E696" t="b">
@@ -23999,22 +24229,22 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 5</t>
+          <t>ACTUATOR ISOLATION STARTUP VENTING BOILER</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E697" t="b">
@@ -24027,22 +24257,22 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0026</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 6</t>
+          <t>ACTUATOR IGV SA FAN 2 10HLB02EX001</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E698" t="b">
@@ -24055,17 +24285,22 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MOV MAIN STEAM DRAIN</t>
+          <t>FLUIDIZING VALVE BED MATERIAL</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E699" t="b">
@@ -24078,22 +24313,22 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>ACTUATOR DESH-1 SPRAY WATER ISOLATION</t>
+          <t>FLUIDIZING VALVE LIMESTONE 1&amp;2</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E700" t="b">
@@ -24106,22 +24341,22 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>WO-100826-0039</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>ACTUATOR DESH-2 SPRAY WATER ISOLATION</t>
+          <t>ACTUATOR STEAM DRUM VENTING ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E701" t="b">
@@ -24134,22 +24369,22 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>ACTUATOR INLET ID FAN 1 MOV 10HNA61AA001</t>
+          <t>ACTUATOR STEAM DRUM MOV VENTING VALVE</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E702" t="b">
@@ -24162,22 +24397,22 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>ACTUATOR OUTLET ID FAN 1 MOV 10HNA71AA001</t>
+          <t>ACTUATOR STEAM DRUM CBD ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E703" t="b">
@@ -24190,12 +24425,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>WO-100826-0020</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV OUTLET PA FAN 1</t>
+          <t>ACTUATOR STEAM DRUM MOV CBD CONTROL VALVE</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -24218,12 +24453,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>WO-100826-0020</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV PA FAN 1</t>
+          <t>ACTUATOR STEAM DRUM IBD ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -24246,12 +24481,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>ACTUATOR ISOLATION STARTUP VENTING BOILER</t>
+          <t>ACTUATOR STEAM DRUM MOV IBD CONTROL VALVE</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -24274,17 +24509,17 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>WO-100826-0026</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>ACTUATOR IGV SA FAN 2 10HLB02EX001</t>
+          <t>ACTUATOR MOV PA FAN2</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -24302,17 +24537,17 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0024</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>FLUIDIZING VALVE BED MATERIAL</t>
+          <t>ACTUATOR MOV OUTLET SA FAN 1</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -24330,17 +24565,17 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>FLUIDIZING VALVE LIMESTONE 1&amp;2</t>
+          <t>ACTUATOR HP BYPASS CONTROL VALVE 10LBF10AA210</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -24358,17 +24593,17 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM VENTING ISOLATION VALVE</t>
+          <t>ACTUATOR BYPASS SPRAY CONTROL VALVE 10LCE40AA210</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -24386,17 +24621,17 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM MOV VENTING VALVE</t>
+          <t>CEP DISCHARGE VALVE</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -24414,12 +24649,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM CBD ISOLATION VALVE</t>
+          <t>MOV MAIN STEAM DRAIN STG-2</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -24442,17 +24677,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM MOV CBD CONTROL VALVE</t>
+          <t>ACTUATOR ON/OFF NRV STEAM EXTRACTION 1, 2, 3</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -24470,17 +24705,17 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM IBD ISOLATION VALVE</t>
+          <t>ACTUATOR ON/OFF VALVE CEP-1 &amp; CEP-2</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -24498,12 +24733,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0037</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM MOV IBD CONTROL VALVE</t>
+          <t>ACTUATOR MOV INLET ECONOMIZER</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -24526,12 +24761,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0037</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV PA FAN2</t>
+          <t>ACTUATOR MOV RECIRCULATION ECONOMIZER</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -24554,22 +24789,22 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>WO-100826-0024</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV OUTLET SA FAN 1</t>
+          <t>10MAA10CP001: PRESSURE BEHIND TURBINE CONTROL</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E717" t="b">
@@ -24582,22 +24817,22 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>ACTUATOR HP BYPASS CONTROL VALVE 10LBF10AA210</t>
+          <t>10MAX45CP004: VALVE BLOCK, OUTLET POSITION LIVE STEAM</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E718" t="b">
@@ -24610,22 +24845,22 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0039</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>ACTUATOR BYPASS SPRAY CONTROL VALVE 10LCE40AA210</t>
+          <t>10HAH46CT001: TEMPERATURE AFTER DESH 2</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E719" t="b">
@@ -24638,21 +24873,26 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0039</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>CEP DISCHARGE VALVE</t>
+          <t>10HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E720" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -24661,22 +24901,22 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>MOV MAIN STEAM DRAIN STG-2</t>
+          <t>10HAH46CT010: TEMPERATURE AFTER DESH 1</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E721" t="b">
@@ -24689,22 +24929,22 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0030</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>ACTUATOR ON/OFF NRV STEAM EXTRACTION 1, 2, 3</t>
+          <t>10HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E722" t="b">
@@ -24717,22 +24957,22 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0030</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>ACTUATOR ON/OFF VALVE CEP-1 &amp; CEP-2</t>
+          <t>10HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E723" t="b">
@@ -24745,22 +24985,22 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>WO-100826-0037</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV INLET ECONOMIZER</t>
+          <t>10HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E724" t="b">
@@ -24773,22 +25013,22 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>WO-100826-0037</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV RECIRCULATION ECONOMIZER</t>
+          <t>10HLB01CP101: DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E725" t="b">
@@ -24801,12 +25041,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>10MAA10CP001: PRESSURE BEHIND TURBINE CONTROL</t>
+          <t>10HLB02CP101: DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -24829,12 +25069,12 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>10MAX45CP004: VALVE BLOCK, OUTLET POSITION LIVE STEAM</t>
+          <t>10LAC10CP101: DP SWITCH BFP 1</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -24857,17 +25097,17 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>WO-100826-0039</t>
+          <t>WO-100826-0036</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>10HAH46CT001: TEMPERATURE AFTER DESH 2</t>
+          <t>10LAC30CP101: DP SWITCH BFP 2</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -24885,22 +25125,22 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>WO-100826-0039</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>10HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
+          <t>ACTUATOR DESH-1 SPRAY WATER CONTROL VALVE</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E729" t="b">
@@ -24913,22 +25153,22 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>10HAH46CT010: TEMPERATURE AFTER DESH 1</t>
+          <t>MOV DISCHARGE BFP-1</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E730" t="b">
@@ -24941,22 +25181,22 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>10HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
+          <t>SOOT BLOWER CONTROL VALVE</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E731" t="b">
@@ -24969,22 +25209,22 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>WO-100826-0030</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>10HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
+          <t>ACTUATOR MOV TURBINE STOP VALVE</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E732" t="b">
@@ -24997,17 +25237,17 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>WO-100826-0030</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>10HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
+          <t>10QEB10CP001: P&amp;S BLOWER PRESS OUTLET</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -25025,17 +25265,17 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>10HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
+          <t>10LAE10CF001: DESH 1 SPRAY WATER FLOW</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -25053,17 +25293,17 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>10HLB01CP101: DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
+          <t>10LAA10CP001: FEEDWATER STORAGE TANK PRESSURE</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -25081,17 +25321,17 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>10HLB02CP101: DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
+          <t>10HGC10CF001: CYCLE MAKE UP PUMP DEAERATOR</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -25109,17 +25349,17 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>10LAC10CP101: DP SWITCH BFP 1</t>
+          <t>10LAA10CL001: DEAERATOR TANK LEVEL 1</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -25137,17 +25377,17 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>WO-100826-0036</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>10LAC30CP101: DP SWITCH BFP 2</t>
+          <t>10LBD10CP001: TURBINE EXTRACTION III TO DEAERATOR PRESSURE</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -25165,22 +25405,22 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>ACTUATOR DESH-1 SPRAY WATER CONTROL VALVE</t>
+          <t>10MAA10CP002: TURBINE EXHAUST PRESSURE</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E739" t="b">
@@ -25198,17 +25438,17 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>MOV DISCHARGE BFP-1</t>
+          <t>10LAA10CT001: FEEDWATER STORAGE TANK</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E740" t="b">
@@ -25221,22 +25461,22 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>SOOT BLOWER CONTROL VALVE</t>
+          <t>10LCC10CT001: LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E741" t="b">
@@ -25254,16 +25494,21 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV TURBINE STOP VALVE</t>
+          <t>10LBS10CT001: TURBINE EXTRACTION I TO LPH1 TEMP</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E742" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -25272,17 +25517,17 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0030</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>10QEB10CP001: P&amp;S BLOWER PRESS OUTLET</t>
+          <t>10HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -25300,17 +25545,17 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>10LAE10CF001: DESH 1 SPRAY WATER FLOW</t>
+          <t>10HBK01CP050: BACKPASS PRESSURE AFTER ECO</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -25328,26 +25573,21 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>10LAA10CP001: FEEDWATER STORAGE TANK PRESSURE</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
+          <t>ACTUATOR TURBINE CONTROL VALVE (GOVERNOR) 10MAA10AA210</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E745" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -25356,17 +25596,17 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>10HGC10CF001: CYCLE MAKE UP PUMP DEAERATOR</t>
+          <t>10HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -25384,17 +25624,17 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>10LAA10CL001: DEAERATOR TANK LEVEL 1</t>
+          <t>10HNA11CT002: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -25412,17 +25652,17 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>10LBD10CP001: TURBINE EXTRACTION III TO DEAERATOR PRESSURE</t>
+          <t>10HNA11CT003: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -25440,17 +25680,17 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>10MAA10CP002: TURBINE EXHAUST PRESSURE</t>
+          <t>10HNA01CT001: INLET CYCLONE</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -25462,169 +25702,6 @@
         <v>1</v>
       </c>
       <c r="H749" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>WO-100826-0045</t>
-        </is>
-      </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>10LAA10CT001: FEEDWATER STORAGE TANK</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>JAPA</t>
-        </is>
-      </c>
-      <c r="E750" t="b">
-        <v>1</v>
-      </c>
-      <c r="H750" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>WO-100826-0045</t>
-        </is>
-      </c>
-      <c r="B751" t="inlineStr">
-        <is>
-          <t>10LCC10CT001: LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP</t>
-        </is>
-      </c>
-      <c r="C751" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>JAPA</t>
-        </is>
-      </c>
-      <c r="E751" t="b">
-        <v>1</v>
-      </c>
-      <c r="H751" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>WO-100826-0045</t>
-        </is>
-      </c>
-      <c r="B752" t="inlineStr">
-        <is>
-          <t>10LBS10CT001: TURBINE EXTRACTION I TO LPH1 TEMP</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>JAPA</t>
-        </is>
-      </c>
-      <c r="E752" t="b">
-        <v>1</v>
-      </c>
-      <c r="H752" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>WO-100826-0030</t>
-        </is>
-      </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>10HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="D753" t="inlineStr">
-        <is>
-          <t>JAPA</t>
-        </is>
-      </c>
-      <c r="E753" t="b">
-        <v>1</v>
-      </c>
-      <c r="H753" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>WO-100826-0074</t>
-        </is>
-      </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>10HBK01CP050: BACKPASS PRESSURE AFTER ECO</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>JAPA</t>
-        </is>
-      </c>
-      <c r="E754" t="b">
-        <v>1</v>
-      </c>
-      <c r="H754" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>WO-100826-0057</t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>ACTUATOR TURBINE CONTROL VALVE (GOVERNOR) 10MAA10AA210</t>
-        </is>
-      </c>
-      <c r="D755" t="inlineStr">
-        <is>
-          <t>AMP</t>
-        </is>
-      </c>
-      <c r="E755" t="b">
-        <v>0</v>
-      </c>
-      <c r="H755" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26441,7 +26518,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J14" t="b">
@@ -26455,7 +26532,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
     </row>
@@ -29020,7 +29097,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -29693,17 +29770,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -30826,8 +30908,13 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -32275,7 +32362,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -32463,7 +32550,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -33353,7 +33440,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H56" t="b">
@@ -33494,7 +33581,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -33588,7 +33675,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -33635,7 +33722,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H62" t="b">
@@ -33682,7 +33769,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H63" t="b">
@@ -33870,7 +33957,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H67" t="b">
@@ -34771,11 +34858,19 @@
           <t>0 - 2500 mmH20</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
+      </c>
+      <c r="M86" t="b">
+        <v>1</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -34812,7 +34907,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -34859,7 +34954,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H88" t="b">
@@ -35240,7 +35335,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -35250,11 +35345,11 @@
         <v>0</v>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
     </row>
@@ -35287,7 +35382,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -35297,11 +35392,11 @@
         <v>0</v>
       </c>
       <c r="M7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
     </row>
@@ -35334,7 +35429,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -35344,11 +35439,11 @@
         <v>0</v>
       </c>
       <c r="M8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
     </row>
@@ -35379,14 +35474,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -35421,14 +35521,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -35463,14 +35568,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -35505,14 +35615,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -35547,14 +35662,19 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -35589,14 +35709,19 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -35631,14 +35756,19 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -35673,14 +35803,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -35715,14 +35850,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -35757,14 +35897,19 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -35799,11 +35944,19 @@
           <t>0-150 °C</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -36092,11 +36245,19 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -36143,7 +36304,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -36178,11 +36339,19 @@
           <t>0-300 °C</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -36217,11 +36386,19 @@
           <t>0-300 °C</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -36342,11 +36519,19 @@
           <t>0-300 °C</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -36381,11 +36566,19 @@
           <t>0-150 °C</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -2270,9 +2270,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2284,7 +2289,7 @@
         <v>21</v>
       </c>
       <c r="L20" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2565,9 +2570,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2927,9 +2937,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2941,7 +2956,7 @@
         <v>38</v>
       </c>
       <c r="L31" t="n">
-        <v>81.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -3155,9 +3170,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3169,7 +3189,7 @@
         <v>55</v>
       </c>
       <c r="L35" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3207,9 +3227,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3221,7 +3246,7 @@
         <v>13</v>
       </c>
       <c r="L36" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3383,9 +3408,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3397,7 +3427,7 @@
         <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3621,9 +3651,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3849,9 +3884,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3863,7 +3903,7 @@
         <v>8</v>
       </c>
       <c r="L47" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -3901,9 +3941,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3915,7 +3960,7 @@
         <v>8</v>
       </c>
       <c r="L48" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3960,7 +4005,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3972,13 +4017,14 @@
         <v>8</v>
       </c>
       <c r="L49" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -4124,9 +4170,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4138,7 +4189,7 @@
         <v>5</v>
       </c>
       <c r="L52" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4476,9 +4527,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4490,7 +4546,7 @@
         <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -9668,13 +9724,18 @@
           <t>INSPECTION OF IGNITER GUN</t>
         </is>
       </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -9691,13 +9752,18 @@
           <t>INSPECTION OF START UP BURNER SKID DEVICE</t>
         </is>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -9910,13 +9976,18 @@
           <t>ACTUATOR SKID BURNER MAIN LDO LINE CONTROL VALVE</t>
         </is>
       </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -9933,13 +10004,18 @@
           <t>ACTUATOR SKID BURNER 1 LDO LINE CONTROL VALVE</t>
         </is>
       </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -9956,13 +10032,18 @@
           <t>ACTUATOR SKID BURNER 1 ATOMISING AIR LINE CONTROL VALVE</t>
         </is>
       </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -9979,13 +10060,18 @@
           <t>ACTUATOR SUB BURNER 1 VALVE 10HJN11AA003</t>
         </is>
       </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -10002,13 +10088,18 @@
           <t>ACTUATOR SKID BURNER 1 ATOM AIR ISOLATION VALVE</t>
         </is>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -10025,13 +10116,18 @@
           <t>ACTUATOR SKID BURNER 1 LDO ISOLATION VALVE</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -10048,13 +10144,18 @@
           <t>ACTUATOR SKID BURNER 1 SCAVENGING VALVE</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -13755,13 +13856,18 @@
           <t>CLEANING BODY GENERATOR</t>
         </is>
       </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D318" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -13974,13 +14080,18 @@
           <t>INSPECTION ROTOR GROUNDING</t>
         </is>
       </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E326" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14137,13 +14248,18 @@
           <t>ASSEMBLY OIL DEFLECTOR BEARING</t>
         </is>
       </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E332" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14440,13 +14556,18 @@
           <t>INSPECTION DISCONNECTING SWITCH NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D343" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E343" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -14463,13 +14584,18 @@
           <t>INSPECTION TRAFO NETRAL GROUNDING RESISTANCE (NGR)</t>
         </is>
       </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D344" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E344" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -14654,13 +14780,18 @@
           <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D351" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E351" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -14677,13 +14808,18 @@
           <t>CLEANING</t>
         </is>
       </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D352" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -16212,13 +16348,18 @@
           <t>TURBINE EXTRACTION III TO DEAERATOR TEMPERATURE TRANSMITTER (20LBD20CT001)</t>
         </is>
       </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D407" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E407" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -16235,13 +16376,18 @@
           <t>TURBINE EXTRACTION I TO LPH1 TEMPERATURE TRANSMITTER (20LBD10CT001)</t>
         </is>
       </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D408" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E408" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -17238,13 +17384,18 @@
           <t>MSW00CYE10GH105 : ALARM SYSTEM CHP MCC</t>
         </is>
       </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D444" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -17877,13 +18028,18 @@
           <t>PM panel RIO</t>
         </is>
       </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
       <c r="D467" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E467" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -18574,7 +18730,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -18602,7 +18758,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -19524,13 +19680,18 @@
           <t>VALVE CHEST TEMPERATURE TRANSMITTER 10MAA10CT011</t>
         </is>
       </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D526" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E526" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -19603,13 +19764,18 @@
           <t>HP BYPASS TEMPERATURE TRANSMITTER 10LBF10CT001</t>
         </is>
       </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D529" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E529" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -19626,13 +19792,18 @@
           <t>BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
         </is>
       </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D530" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E530" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -19705,13 +19876,18 @@
           <t>MSW10LBF10CT101 : UNIT 1 STEAM BYPASS REDUCING TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D533" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E533" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -19784,13 +19960,18 @@
           <t>TURBINE DRAIN VALVE AFTER FIRST STAGE 10MAL30AA210</t>
         </is>
       </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D536" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E536" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -19807,13 +19988,18 @@
           <t>TURBINE DRAIN VALVE 10MAL40AA210</t>
         </is>
       </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D537" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E537" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -19830,13 +20016,18 @@
           <t>TURBINE DRAIN VALVE 10MAL50AA210</t>
         </is>
       </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D538" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E538" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -19853,13 +20044,18 @@
           <t>TURBINE DRAIN VALVE 10MAL60AA210</t>
         </is>
       </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D539" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E539" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -19876,13 +20072,18 @@
           <t>TURBINE DRAIN VALVE 10MAL70AA210</t>
         </is>
       </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D540" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E540" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -20151,13 +20352,18 @@
           <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB11CT001</t>
         </is>
       </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D550" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E550" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -20174,13 +20380,18 @@
           <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB12CT001</t>
         </is>
       </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D551" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E551" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -20197,13 +20408,18 @@
           <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB21CT001</t>
         </is>
       </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D552" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E552" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -20220,13 +20436,18 @@
           <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB22CT001</t>
         </is>
       </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="D553" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -21839,13 +22060,18 @@
           <t>PM panel RIO</t>
         </is>
       </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
       <c r="D611" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E611" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -24051,6 +24277,7 @@
           <t>31/08/2026</t>
         </is>
       </c>
+      <c r="D690" t="inlineStr"/>
       <c r="E690" t="b">
         <v>1</v>
       </c>
@@ -24435,7 +24662,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -24491,7 +24718,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -25581,13 +25808,18 @@
           <t>ACTUATOR TURBINE CONTROL VALVE (GOVERNOR) 10MAA10AA210</t>
         </is>
       </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="D745" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E745" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -28391,7 +28623,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -28760,7 +28992,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -29250,17 +29482,22 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -29359,17 +29596,22 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -29411,17 +29653,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -29463,17 +29710,22 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -29515,17 +29767,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -29567,17 +29824,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -30035,17 +30297,22 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -30087,17 +30354,22 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -30134,17 +30406,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -30181,17 +30458,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -30228,17 +30510,22 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -30275,17 +30562,22 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -30322,17 +30614,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -30369,17 +30666,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -30416,17 +30718,22 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -30463,17 +30770,22 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -30510,17 +30822,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -30557,17 +30874,22 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -30604,17 +30926,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -30760,17 +31087,22 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -34380,7 +34712,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -35523,7 +35855,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -35570,7 +35902,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -36038,14 +36370,19 @@
           <t>0-60 °C</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -36080,14 +36417,19 @@
           <t>0-60 °C</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -36122,14 +36464,19 @@
           <t>0-60 °C</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -36164,14 +36511,19 @@
           <t>0-60 °C</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -36206,11 +36558,19 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -36433,11 +36793,19 @@
           <t>0-600</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -37268,12 +37636,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="T9" t="n">

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -2327,9 +2327,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2341,7 +2346,7 @@
         <v>13</v>
       </c>
       <c r="L21" t="n">
-        <v>38.5</v>
+        <v>100</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -4024,7 +4029,6 @@
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -7150,7 +7154,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10228,13 +10232,18 @@
           <t>INSPECTION OF IGNITER GUN</t>
         </is>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -10251,13 +10260,18 @@
           <t>INSPECTION OF START UP BURNER SKID DEVICE</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -10414,13 +10428,18 @@
           <t>ACTUATOR SKID BURNER 2 LDO LINE CONTROL VALVE</t>
         </is>
       </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -10437,13 +10456,18 @@
           <t>ACTUATOR SKID BURNER 2 ATOMISING AIR LINE CONTROL VALVE</t>
         </is>
       </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -10460,13 +10484,18 @@
           <t>ACTUATOR SKID BURNER 2 ATOM AIR ISOLATION VALVE</t>
         </is>
       </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -10483,13 +10512,18 @@
           <t>ACTUATOR SKID BURNER 2 LDO ISOLATION VALVE</t>
         </is>
       </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -10506,13 +10540,18 @@
           <t>ACTUATOR SKID BURNER 2 SCAVENGING VALVE</t>
         </is>
       </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D198" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -10529,13 +10568,18 @@
           <t>ACTUATOR SUB BURNER 2 VALVE 10HJN12AA003</t>
         </is>
       </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
       <c r="D199" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -24277,7 +24321,6 @@
           <t>31/08/2026</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
       <c r="E690" t="b">
         <v>1</v>
       </c>
@@ -24354,7 +24397,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -30305,7 +30348,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -30362,7 +30405,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -30414,7 +30457,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -30466,7 +30509,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -30518,7 +30561,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -30570,7 +30613,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -30622,7 +30665,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -30674,7 +30717,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -30726,7 +30769,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J87" t="b">
@@ -30778,7 +30821,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -30830,7 +30873,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J89" t="b">
@@ -30882,7 +30925,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J90" t="b">
@@ -30934,7 +30977,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J91" t="b">
@@ -31242,14 +31285,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -39152,7 +39205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -39224,7 +39277,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -39659,7 +39712,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Actuator Valve</t>
+          <t>21. Remote Control Panel (RCP)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -39672,14 +39725,9 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -39689,7 +39737,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>21. Remote Control Panel (RCP)</t>
+          <t>22. Busduct Trafo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -39699,76 +39747,81 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>M ZAINI</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>22. Busduct Trafo</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>INSULATION RESISTANCE TEST, kontak
 resistan bagian konduktor,
 grounding check</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>M IQBAL</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>23. Busduct Generator</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>INSULATION RESISTANCE TEST, kontak
 resistan bagian konduktor,
 grounding check</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>M IQBAL</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>24. MV Motor Cable 6.6 kV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -39778,7 +39831,7 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>24. MV Motor Cable 6.6 kV</t>
+          <t>25. LV Motor Cable 380 V</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -39798,7 +39851,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -39808,7 +39861,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>25. LV Motor Cable 380 V</t>
+          <t>26. Electrical Grounding</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -39823,12 +39876,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
+          <t>Visual inspection on connections and damage, tightening &amp; cleaning, grounding resistance measurement and verification</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>YOGA</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -39838,7 +39891,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>26. Electrical Grounding</t>
+          <t>1. Panel DCS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -39853,12 +39906,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Visual inspection on connections and damage, tightening &amp; cleaning, grounding resistance measurement and verification</t>
+          <t>Physical inspection of panel (cleanliness, doors, locks, grounding), CPU/I/O/Power Supply LED indicators, panel temperature, and ensuring no active alarms or system faults.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>YOGA</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -39868,7 +39921,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>1. Panel DCS</t>
+          <t>2. Pressure tx range -70~1500 mBar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39883,12 +39936,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Physical inspection of panel (cleanliness, doors, locks, grounding), CPU/I/O/Power Supply LED indicators, panel temperature, and ensuring no active alarms or system faults.</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -39898,7 +39951,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2. Pressure tx range -70~1500 mBar</t>
+          <t>3. Pressure tx range -1~180 Bar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -39928,7 +39981,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>3. Pressure tx range -1~180 Bar</t>
+          <t>4. Flow tx range -500~12500 mmH2O</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -39958,7 +40011,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>4. Flow tx range -500~12500 mmH2O</t>
+          <t>5. Temperature tx range 0 ~ 1200 celcius</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -39988,17 +40041,17 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>5. Temperature tx range 0 ~ 1200 celcius</t>
+          <t>PRESSURE SWITCH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -40018,17 +40071,17 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Actuator Valve</t>
+          <t>ACTUATOR ON OFF VALVE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>General Inspection</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -40038,7 +40091,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -40048,7 +40101,7 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unit 1 - GCB Panel Cooling Fan Blower replacement (Mx)</t>
+          <t>IGV CONTROL (SA, SUB)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -40058,7 +40111,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>General Inspection</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -40068,7 +40121,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -40078,7 +40131,7 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH</t>
+          <t>GOVERNOR VALVE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -40088,17 +40141,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>General Inspection</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Verification &amp; Calibration</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Verification &amp; Calibration</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -40108,7 +40161,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>ACTUATOR ON OFF VALVE</t>
+          <t>ACTUATOR CONTROL VALVE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -40128,7 +40181,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -40138,7 +40191,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>IGV CONTROL (SA, SUB)</t>
+          <t>ACTUATOR MOTORIZED VALVE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -40158,7 +40211,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -40168,7 +40221,7 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>GOVERNOR VALVE</t>
+          <t>LEVEL SWITCH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -40178,7 +40231,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>General Inspection</t>
+          <t>Verification &amp; Function Test</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -40188,7 +40241,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -40198,7 +40251,7 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>ACTUATOR CONTROL VALVE</t>
+          <t>FIRE ALARM SYSTEM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -40208,7 +40261,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>General Inspection</t>
+          <t>Verification &amp; Function Test</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -40222,96 +40275,6 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ACTUATOR MOTORIZED VALVE</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>MSW</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>General Inspection</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Verification &amp; Calibration</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>M TOHER</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LEVEL SWITCH</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>MSW</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Verification &amp; Function Test</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Verification &amp; Calibration</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>FERRYUS</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FIRE ALARM SYSTEM</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>MSW</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Verification &amp; Function Test</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Verification &amp; Calibration</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>M TOHER</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -159,6 +159,7 @@
       <bottom style="thin">
         <color rgb="00D3D3D3"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -7154,7 +7155,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12670,7 +12671,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -24397,7 +24398,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -26124,7 +26125,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -31285,7 +31286,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="H2" t="b">
